--- a/Sample_run/1/student/KienTTHE186727/TC4/GradeDetail.xlsx
+++ b/Sample_run/1/student/KienTTHE186727/TC4/GradeDetail.xlsx
@@ -1062,7 +1062,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>40682</x:v>
+        <x:v>51684</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1121,7 +1121,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>40682</x:v>
+        <x:v>51684</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1174,7 +1174,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>40682</x:v>
+        <x:v>51684</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1230,7 +1230,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>40682</x:v>
+        <x:v>51684</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1289,7 +1289,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>40682</x:v>
+        <x:v>51684</x:v>
       </x:c>
       <x:c r="R6" s="2" t="s">
         <x:v>46</x:v>
@@ -1678,7 +1678,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P13" s="0">
-        <x:v>48566</x:v>
+        <x:v>54892</x:v>
       </x:c>
       <x:c r="Q13" s="0">
         <x:v>4000</x:v>
@@ -1737,7 +1737,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q14" s="0">
-        <x:v>48566</x:v>
+        <x:v>54892</x:v>
       </x:c>
       <x:c r="R14" s="4" t="s">
         <x:v>61</x:v>
@@ -1790,7 +1790,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P15" s="0">
-        <x:v>48566</x:v>
+        <x:v>54892</x:v>
       </x:c>
       <x:c r="Q15" s="0">
         <x:v>4000</x:v>
